--- a/Fase 2/SIGMA_Product_Backlog_por_Sprint.xlsx
+++ b/Fase 2/SIGMA_Product_Backlog_por_Sprint.xlsx
@@ -11342,7 +11342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G391"/>
+  <dimension ref="A1:G409"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="26" min="1" max="1"/>
@@ -25604,6 +25604,659 @@
         <is>
           <t>Cuando abro una importación
 Entonces veo las filas procesadas y los registros que se crearon a partir de ella</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="12" t="inlineStr">
+        <is>
+          <t>HU-059</t>
+        </is>
+      </c>
+      <c r="B392" s="13" t="inlineStr">
+        <is>
+          <t>Saber en qué estante y de qué lote está cada repuesto</t>
+        </is>
+      </c>
+      <c r="C392" s="12" t="inlineStr">
+        <is>
+          <t>EP-06</t>
+        </is>
+      </c>
+      <c r="D392" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="E392" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F392" s="13" t="inlineStr">
+        <is>
+          <t>Ingreso con estante y lote</t>
+        </is>
+      </c>
+      <c r="G392" s="13" t="inlineStr">
+        <is>
+          <t>Dado que la bodega tiene ubicaciones
+Cuando registro un ingreso sin indicar en qué estante queda
+Entonces se rechaza; con estante y lote, la existencia queda en ese cubo (bodega, ubicación, lote)</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="12" t="inlineStr">
+        <is>
+          <t>HU-059</t>
+        </is>
+      </c>
+      <c r="B393" s="13" t="inlineStr">
+        <is>
+          <t>Saber en qué estante y de qué lote está cada repuesto</t>
+        </is>
+      </c>
+      <c r="C393" s="12" t="inlineStr">
+        <is>
+          <t>EP-06</t>
+        </is>
+      </c>
+      <c r="D393" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="E393" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F393" s="13" t="inlineStr">
+        <is>
+          <t>Existencias por estante y lote</t>
+        </is>
+      </c>
+      <c r="G393" s="13" t="inlineStr">
+        <is>
+          <t>Cuando consulto las existencias
+Entonces veo la cantidad desglosada por bodega, ubicación y lote, y el umbral mínimo se evalúa por bodega</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="12" t="inlineStr">
+        <is>
+          <t>HU-059</t>
+        </is>
+      </c>
+      <c r="B394" s="13" t="inlineStr">
+        <is>
+          <t>Saber en qué estante y de qué lote está cada repuesto</t>
+        </is>
+      </c>
+      <c r="C394" s="12" t="inlineStr">
+        <is>
+          <t>EP-06</t>
+        </is>
+      </c>
+      <c r="D394" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="E394" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F394" s="13" t="inlineStr">
+        <is>
+          <t>Reubicación dentro de la bodega</t>
+        </is>
+      </c>
+      <c r="G394" s="13" t="inlineStr">
+        <is>
+          <t>Cuando muevo un repuesto de un estante a otro de la misma bodega
+Entonces la existencia cambia de ubicación con un solo movimiento (sin salida ni entrada) y queda el historial de ubicaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="12" t="inlineStr">
+        <is>
+          <t>HU-059</t>
+        </is>
+      </c>
+      <c r="B395" s="13" t="inlineStr">
+        <is>
+          <t>Saber en qué estante y de qué lote está cada repuesto</t>
+        </is>
+      </c>
+      <c r="C395" s="12" t="inlineStr">
+        <is>
+          <t>EP-06</t>
+        </is>
+      </c>
+      <c r="D395" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="E395" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F395" s="13" t="inlineStr">
+        <is>
+          <t>Trazabilidad del lote</t>
+        </is>
+      </c>
+      <c r="G395" s="13" t="inlineStr">
+        <is>
+          <t>Cuando consulto un lote
+Entonces veo cuánto ingresó, cuánto se consumió y cuánto queda, con su vencimiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="12" t="inlineStr">
+        <is>
+          <t>HU-066</t>
+        </is>
+      </c>
+      <c r="B396" s="13" t="inlineStr">
+        <is>
+          <t>Identificar bodegas, ubicaciones y repuestos con etiquetas QR</t>
+        </is>
+      </c>
+      <c r="C396" s="12" t="inlineStr">
+        <is>
+          <t>EP-06</t>
+        </is>
+      </c>
+      <c r="D396" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="E396" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F396" s="13" t="inlineStr">
+        <is>
+          <t>Etiquetas de una bodega</t>
+        </is>
+      </c>
+      <c r="G396" s="13" t="inlineStr">
+        <is>
+          <t>Cuando elijo una bodega en el centro de etiquetas e imprimo sus ubicaciones
+Entonces obtengo una hoja con una etiqueta por ubicación, cada una con su código y su QR</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="12" t="inlineStr">
+        <is>
+          <t>HU-066</t>
+        </is>
+      </c>
+      <c r="B397" s="13" t="inlineStr">
+        <is>
+          <t>Identificar bodegas, ubicaciones y repuestos con etiquetas QR</t>
+        </is>
+      </c>
+      <c r="C397" s="12" t="inlineStr">
+        <is>
+          <t>EP-06</t>
+        </is>
+      </c>
+      <c r="D397" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="E397" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F397" s="13" t="inlineStr">
+        <is>
+          <t>Formato de papel</t>
+        </is>
+      </c>
+      <c r="G397" s="13" t="inlineStr">
+        <is>
+          <t>Cuando cambio el formato de papel
+Entonces la hoja se reacomoda al formato elegido y el código se lee completo, sin recortarse</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="12" t="inlineStr">
+        <is>
+          <t>HU-066</t>
+        </is>
+      </c>
+      <c r="B398" s="13" t="inlineStr">
+        <is>
+          <t>Identificar bodegas, ubicaciones y repuestos con etiquetas QR</t>
+        </is>
+      </c>
+      <c r="C398" s="12" t="inlineStr">
+        <is>
+          <t>EP-06</t>
+        </is>
+      </c>
+      <c r="D398" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="E398" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F398" s="13" t="inlineStr">
+        <is>
+          <t>Sin permiso</t>
+        </is>
+      </c>
+      <c r="G398" s="13" t="inlineStr">
+        <is>
+          <t>Dado que no tengo el permiso IMPRIMIR ETIQUETAS
+Cuando entro al centro de etiquetas
+Entonces no se me ofrece nada para imprimir</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="12" t="inlineStr">
+        <is>
+          <t>HU-067</t>
+        </is>
+      </c>
+      <c r="B399" s="13" t="inlineStr">
+        <is>
+          <t>Consultar escaneando una etiqueta</t>
+        </is>
+      </c>
+      <c r="C399" s="12" t="inlineStr">
+        <is>
+          <t>EP-06</t>
+        </is>
+      </c>
+      <c r="D399" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="E399" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F399" s="13" t="inlineStr">
+        <is>
+          <t>Consulta de una ubicación</t>
+        </is>
+      </c>
+      <c r="G399" s="13" t="inlineStr">
+        <is>
+          <t>Cuando escaneo o escribo el código de una ubicación
+Entonces veo qué repuestos hay en ese estante, con cantidad y lote</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="12" t="inlineStr">
+        <is>
+          <t>HU-067</t>
+        </is>
+      </c>
+      <c r="B400" s="13" t="inlineStr">
+        <is>
+          <t>Consultar escaneando una etiqueta</t>
+        </is>
+      </c>
+      <c r="C400" s="12" t="inlineStr">
+        <is>
+          <t>EP-06</t>
+        </is>
+      </c>
+      <c r="D400" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="E400" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F400" s="13" t="inlineStr">
+        <is>
+          <t>Bodega y repuesto</t>
+        </is>
+      </c>
+      <c r="G400" s="13" t="inlineStr">
+        <is>
+          <t>Cuando el código es de una bodega o de un repuesto
+Entonces la misma pantalla muestra su desglose (por ubicación o por bodega)</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="12" t="inlineStr">
+        <is>
+          <t>HU-067</t>
+        </is>
+      </c>
+      <c r="B401" s="13" t="inlineStr">
+        <is>
+          <t>Consultar escaneando una etiqueta</t>
+        </is>
+      </c>
+      <c r="C401" s="12" t="inlineStr">
+        <is>
+          <t>EP-06</t>
+        </is>
+      </c>
+      <c r="D401" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="E401" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F401" s="13" t="inlineStr">
+        <is>
+          <t>Código no reconocido</t>
+        </is>
+      </c>
+      <c r="G401" s="13" t="inlineStr">
+        <is>
+          <t>Cuando el código no corresponde a nada del cliente
+Entonces se informa con claridad y no se muestra información de otro cliente</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="12" t="inlineStr">
+        <is>
+          <t>HU-068</t>
+        </is>
+      </c>
+      <c r="B402" s="13" t="inlineStr">
+        <is>
+          <t>Cargar y descargar el maestro de repuestos en planilla</t>
+        </is>
+      </c>
+      <c r="C402" s="12" t="inlineStr">
+        <is>
+          <t>EP-06</t>
+        </is>
+      </c>
+      <c r="D402" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="E402" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F402" s="13" t="inlineStr">
+        <is>
+          <t>Carga desde la plantilla</t>
+        </is>
+      </c>
+      <c r="G402" s="13" t="inlineStr">
+        <is>
+          <t>Cuando descargo la plantilla, la completo y la cargo
+Entonces las filas válidas se crean; una fila mala no detiene el resto y se informa cuál falló y por qué</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="12" t="inlineStr">
+        <is>
+          <t>HU-068</t>
+        </is>
+      </c>
+      <c r="B403" s="13" t="inlineStr">
+        <is>
+          <t>Cargar y descargar el maestro de repuestos en planilla</t>
+        </is>
+      </c>
+      <c r="C403" s="12" t="inlineStr">
+        <is>
+          <t>EP-06</t>
+        </is>
+      </c>
+      <c r="D403" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="E403" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F403" s="13" t="inlineStr">
+        <is>
+          <t>Descarga a Excel</t>
+        </is>
+      </c>
+      <c r="G403" s="13" t="inlineStr">
+        <is>
+          <t>Cuando descargo a Excel desde el listado
+Entonces bajan los repuestos que coinciden con la búsqueda</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="12" t="inlineStr">
+        <is>
+          <t>HU-069</t>
+        </is>
+      </c>
+      <c r="B404" s="13" t="inlineStr">
+        <is>
+          <t>Generar los códigos automáticamente</t>
+        </is>
+      </c>
+      <c r="C404" s="12" t="inlineStr">
+        <is>
+          <t>EP-06</t>
+        </is>
+      </c>
+      <c r="D404" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="E404" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F404" s="13" t="inlineStr">
+        <is>
+          <t>Código generado</t>
+        </is>
+      </c>
+      <c r="G404" s="13" t="inlineStr">
+        <is>
+          <t>Cuando creo un registro sin escribir el código
+Entonces el sistema lo genera con el prefijo de su módulo y el id (por ejemplo REP-44)</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="12" t="inlineStr">
+        <is>
+          <t>HU-069</t>
+        </is>
+      </c>
+      <c r="B405" s="13" t="inlineStr">
+        <is>
+          <t>Generar los códigos automáticamente</t>
+        </is>
+      </c>
+      <c r="C405" s="12" t="inlineStr">
+        <is>
+          <t>EP-06</t>
+        </is>
+      </c>
+      <c r="D405" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="E405" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F405" s="13" t="inlineStr">
+        <is>
+          <t>Códigos propios y antiguos</t>
+        </is>
+      </c>
+      <c r="G405" s="13" t="inlineStr">
+        <is>
+          <t>Dado un registro con código escrito a mano
+Cuando se guarda o se edita
+Entonces el código se conserva tal cual</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="12" t="inlineStr">
+        <is>
+          <t>HU-077</t>
+        </is>
+      </c>
+      <c r="B406" s="13" t="inlineStr">
+        <is>
+          <t>Que el sistema avise lo que encuentra</t>
+        </is>
+      </c>
+      <c r="C406" s="12" t="inlineStr">
+        <is>
+          <t>EP-06</t>
+        </is>
+      </c>
+      <c r="D406" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="E406" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F406" s="13" t="inlineStr">
+        <is>
+          <t>Quiebre de stock detectado</t>
+        </is>
+      </c>
+      <c r="G406" s="13" t="inlineStr">
+        <is>
+          <t>Dado un repuesto con existencia bajo el mínimo
+Cuando corre el detector de inventario
+Entonces se abre una alerta de stock mínimo con su severidad (sin existencia es crítica)</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="12" t="inlineStr">
+        <is>
+          <t>HU-077</t>
+        </is>
+      </c>
+      <c r="B407" s="13" t="inlineStr">
+        <is>
+          <t>Que el sistema avise lo que encuentra</t>
+        </is>
+      </c>
+      <c r="C407" s="12" t="inlineStr">
+        <is>
+          <t>EP-06</t>
+        </is>
+      </c>
+      <c r="D407" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="E407" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F407" s="13" t="inlineStr">
+        <is>
+          <t>Sin duplicados y cierre automático</t>
+        </is>
+      </c>
+      <c r="G407" s="13" t="inlineStr">
+        <is>
+          <t>Cuando el detector vuelve a correr sin cambios
+Entonces no duplica; cuando la existencia se repone
+Entonces la alerta se cierra sola como resuelta</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="12" t="inlineStr">
+        <is>
+          <t>HU-077</t>
+        </is>
+      </c>
+      <c r="B408" s="13" t="inlineStr">
+        <is>
+          <t>Que el sistema avise lo que encuentra</t>
+        </is>
+      </c>
+      <c r="C408" s="12" t="inlineStr">
+        <is>
+          <t>EP-06</t>
+        </is>
+      </c>
+      <c r="D408" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="E408" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F408" s="13" t="inlineStr">
+        <is>
+          <t>Aviso en la web</t>
+        </is>
+      </c>
+      <c r="G408" s="13" t="inlineStr">
+        <is>
+          <t>Cuando hay alertas sin leer
+Entonces la campana muestra el contador y la bandeja las agrupa por categoría y gravedad</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="12" t="inlineStr">
+        <is>
+          <t>HU-077</t>
+        </is>
+      </c>
+      <c r="B409" s="13" t="inlineStr">
+        <is>
+          <t>Que el sistema avise lo que encuentra</t>
+        </is>
+      </c>
+      <c r="C409" s="12" t="inlineStr">
+        <is>
+          <t>EP-06</t>
+        </is>
+      </c>
+      <c r="D409" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="E409" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F409" s="13" t="inlineStr">
+        <is>
+          <t>La app recibe lo mismo</t>
+        </is>
+      </c>
+      <c r="G409" s="13" t="inlineStr">
+        <is>
+          <t>Cuando la app consulta GET /alertas y /alertas/resumen
+Entonces recibe las mismas alertas y el mismo contador que la web</t>
         </is>
       </c>
     </row>

--- a/Fase 2/SIGMA_Product_Backlog_por_Sprint.xlsx
+++ b/Fase 2/SIGMA_Product_Backlog_por_Sprint.xlsx
@@ -51826,7 +51826,7 @@
       </c>
       <c r="M6" s="9" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="N6" s="10" t="inlineStr">
@@ -51901,7 +51901,7 @@
       </c>
       <c r="M7" s="12" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="N7" s="13" t="inlineStr">
@@ -51976,7 +51976,7 @@
       </c>
       <c r="M8" s="9" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="N8" s="10" t="inlineStr">
@@ -52051,7 +52051,7 @@
       </c>
       <c r="M9" s="12" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="N9" s="13" t="inlineStr">
@@ -52126,7 +52126,7 @@
       </c>
       <c r="M10" s="9" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="N10" s="10" t="inlineStr">
@@ -52201,7 +52201,7 @@
       </c>
       <c r="M11" s="12" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="N11" s="13" t="inlineStr">
@@ -52276,7 +52276,7 @@
       </c>
       <c r="M12" s="9" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="N12" s="10" t="inlineStr">
@@ -52351,7 +52351,7 @@
       </c>
       <c r="M13" s="12" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="N13" s="13" t="inlineStr">
@@ -52426,7 +52426,7 @@
       </c>
       <c r="M14" s="9" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="N14" s="10" t="inlineStr">
@@ -52501,7 +52501,7 @@
       </c>
       <c r="M15" s="12" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="N15" s="13" t="inlineStr">
@@ -52576,7 +52576,7 @@
       </c>
       <c r="M16" s="9" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="N16" s="10" t="inlineStr">
@@ -52651,7 +52651,7 @@
       </c>
       <c r="M17" s="12" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="N17" s="13" t="inlineStr">
@@ -52726,7 +52726,7 @@
       </c>
       <c r="M18" s="9" t="inlineStr">
         <is>
-          <t>Bloqueada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="N18" s="10" t="inlineStr">
@@ -52801,7 +52801,7 @@
       </c>
       <c r="M19" s="12" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="N19" s="13" t="inlineStr">
@@ -52876,7 +52876,7 @@
       </c>
       <c r="M20" s="9" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="N20" s="10" t="inlineStr">
@@ -52951,7 +52951,7 @@
       </c>
       <c r="M21" s="12" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="N21" s="13" t="inlineStr">
@@ -53026,7 +53026,7 @@
       </c>
       <c r="M22" s="9" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="N22" s="10" t="inlineStr">
@@ -53355,10 +53355,14 @@
       </c>
       <c r="M6" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N6" s="10" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
       <c r="O6" s="9">
         <f>IF($M6="Terminada",$I6,0)</f>
         <v/>
@@ -53422,10 +53426,14 @@
       </c>
       <c r="M7" s="12" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N7" s="13" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N7" s="13" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
       <c r="O7" s="12">
         <f>IF($M7="Terminada",$I7,0)</f>
         <v/>
@@ -53489,10 +53497,14 @@
       </c>
       <c r="M8" s="12" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N8" s="13" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N8" s="13" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
       <c r="O8" s="12">
         <f>IF($M8="Terminada",$I8,0)</f>
         <v/>
@@ -53556,10 +53568,14 @@
       </c>
       <c r="M9" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N9" s="10" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O9" s="9">
         <f>IF($M9="Terminada",$I9,0)</f>
         <v/>
@@ -53623,10 +53639,14 @@
       </c>
       <c r="M10" s="12" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N10" s="13" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N10" s="13" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
       <c r="O10" s="12">
         <f>IF($M10="Terminada",$I10,0)</f>
         <v/>
@@ -53690,10 +53710,14 @@
       </c>
       <c r="M11" s="12" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N11" s="13" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N11" s="13" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O11" s="12">
         <f>IF($M11="Terminada",$I11,0)</f>
         <v/>
@@ -53757,10 +53781,14 @@
       </c>
       <c r="M12" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N12" s="10" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N12" s="10" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
       <c r="O12" s="9">
         <f>IF($M12="Terminada",$I12,0)</f>
         <v/>
@@ -53824,10 +53852,14 @@
       </c>
       <c r="M13" s="12" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N13" s="13" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N13" s="13" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O13" s="12">
         <f>IF($M13="Terminada",$I13,0)</f>
         <v/>
@@ -53891,10 +53923,14 @@
       </c>
       <c r="M14" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N14" s="10" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N14" s="10" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O14" s="9">
         <f>IF($M14="Terminada",$I14,0)</f>
         <v/>
@@ -53958,10 +53994,14 @@
       </c>
       <c r="M15" s="12" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N15" s="13" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N15" s="13" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O15" s="12">
         <f>IF($M15="Terminada",$I15,0)</f>
         <v/>
@@ -54025,10 +54065,14 @@
       </c>
       <c r="M16" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N16" s="10" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N16" s="10" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O16" s="9">
         <f>IF($M16="Terminada",$I16,0)</f>
         <v/>
@@ -54092,10 +54136,14 @@
       </c>
       <c r="M17" s="12" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N17" s="13" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N17" s="13" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O17" s="12">
         <f>IF($M17="Terminada",$I17,0)</f>
         <v/>
@@ -54159,10 +54207,14 @@
       </c>
       <c r="M18" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N18" s="10" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N18" s="10" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
       <c r="O18" s="9">
         <f>IF($M18="Terminada",$I18,0)</f>
         <v/>
@@ -54226,10 +54278,14 @@
       </c>
       <c r="M19" s="12" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N19" s="13" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N19" s="13" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O19" s="12">
         <f>IF($M19="Terminada",$I19,0)</f>
         <v/>
@@ -54293,10 +54349,14 @@
       </c>
       <c r="M20" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N20" s="10" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N20" s="10" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O20" s="9">
         <f>IF($M20="Terminada",$I20,0)</f>
         <v/>
@@ -54360,10 +54420,14 @@
       </c>
       <c r="M21" s="12" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N21" s="13" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N21" s="13" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
       <c r="O21" s="12">
         <f>IF($M21="Terminada",$I21,0)</f>
         <v/>
@@ -54427,10 +54491,14 @@
       </c>
       <c r="M22" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N22" s="10" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N22" s="10" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
       <c r="O22" s="9">
         <f>IF($M22="Terminada",$I22,0)</f>
         <v/>
@@ -54494,10 +54562,14 @@
       </c>
       <c r="M23" s="12" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N23" s="13" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N23" s="13" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
       <c r="O23" s="12">
         <f>IF($M23="Terminada",$I23,0)</f>
         <v/>
@@ -54819,10 +54891,14 @@
       </c>
       <c r="M6" s="12" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N6" s="13" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N6" s="13" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O6" s="12">
         <f>IF($M6="Terminada",$I6,0)</f>
         <v/>
@@ -54886,10 +54962,14 @@
       </c>
       <c r="M7" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N7" s="10" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O7" s="9">
         <f>IF($M7="Terminada",$I7,0)</f>
         <v/>
@@ -54953,10 +55033,14 @@
       </c>
       <c r="M8" s="12" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N8" s="13" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N8" s="13" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O8" s="12">
         <f>IF($M8="Terminada",$I8,0)</f>
         <v/>
@@ -55020,10 +55104,14 @@
       </c>
       <c r="M9" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N9" s="10" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O9" s="9">
         <f>IF($M9="Terminada",$I9,0)</f>
         <v/>
@@ -55087,10 +55175,14 @@
       </c>
       <c r="M10" s="12" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N10" s="13" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N10" s="13" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O10" s="12">
         <f>IF($M10="Terminada",$I10,0)</f>
         <v/>
@@ -55154,10 +55246,14 @@
       </c>
       <c r="M11" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N11" s="10" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O11" s="9">
         <f>IF($M11="Terminada",$I11,0)</f>
         <v/>
@@ -55221,10 +55317,14 @@
       </c>
       <c r="M12" s="12" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N12" s="13" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N12" s="13" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O12" s="12">
         <f>IF($M12="Terminada",$I12,0)</f>
         <v/>
@@ -55288,10 +55388,14 @@
       </c>
       <c r="M13" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N13" s="10" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O13" s="9">
         <f>IF($M13="Terminada",$I13,0)</f>
         <v/>
@@ -55355,10 +55459,14 @@
       </c>
       <c r="M14" s="12" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N14" s="13" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N14" s="13" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O14" s="12">
         <f>IF($M14="Terminada",$I14,0)</f>
         <v/>
@@ -55422,10 +55530,14 @@
       </c>
       <c r="M15" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N15" s="10" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O15" s="9">
         <f>IF($M15="Terminada",$I15,0)</f>
         <v/>
@@ -55489,10 +55601,14 @@
       </c>
       <c r="M16" s="12" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N16" s="13" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N16" s="13" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O16" s="12">
         <f>IF($M16="Terminada",$I16,0)</f>
         <v/>
@@ -55556,10 +55672,14 @@
       </c>
       <c r="M17" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N17" s="10" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N17" s="10" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O17" s="9">
         <f>IF($M17="Terminada",$I17,0)</f>
         <v/>
@@ -55623,10 +55743,14 @@
       </c>
       <c r="M18" s="12" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N18" s="13" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N18" s="13" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O18" s="12">
         <f>IF($M18="Terminada",$I18,0)</f>
         <v/>
@@ -55690,10 +55814,14 @@
       </c>
       <c r="M19" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N19" s="10" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N19" s="10" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
       <c r="O19" s="9">
         <f>IF($M19="Terminada",$I19,0)</f>
         <v/>
@@ -55757,10 +55885,14 @@
       </c>
       <c r="M20" s="12" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N20" s="13" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N20" s="13" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O20" s="12">
         <f>IF($M20="Terminada",$I20,0)</f>
         <v/>
@@ -55824,10 +55956,14 @@
       </c>
       <c r="M21" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N21" s="10" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N21" s="10" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O21" s="9">
         <f>IF($M21="Terminada",$I21,0)</f>
         <v/>
@@ -55891,10 +56027,14 @@
       </c>
       <c r="M22" s="12" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N22" s="13" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N22" s="13" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O22" s="12">
         <f>IF($M22="Terminada",$I22,0)</f>
         <v/>
@@ -55958,10 +56098,14 @@
       </c>
       <c r="M23" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N23" s="10" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N23" s="10" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O23" s="9">
         <f>IF($M23="Terminada",$I23,0)</f>
         <v/>
@@ -56025,10 +56169,14 @@
       </c>
       <c r="M24" s="12" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N24" s="13" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N24" s="13" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O24" s="12">
         <f>IF($M24="Terminada",$I24,0)</f>
         <v/>
@@ -56092,10 +56240,14 @@
       </c>
       <c r="M25" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N25" s="10" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N25" s="10" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
       <c r="O25" s="9">
         <f>IF($M25="Terminada",$I25,0)</f>
         <v/>
@@ -56159,10 +56311,14 @@
       </c>
       <c r="M26" s="12" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N26" s="13" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N26" s="13" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O26" s="12">
         <f>IF($M26="Terminada",$I26,0)</f>
         <v/>
@@ -56226,10 +56382,14 @@
       </c>
       <c r="M27" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N27" s="10" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="N27" s="10" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O27" s="9">
         <f>IF($M27="Terminada",$I27,0)</f>
         <v/>
@@ -56293,7 +56453,7 @@
       </c>
       <c r="M28" s="9" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="N28" s="10" t="inlineStr">
@@ -56368,7 +56528,7 @@
       </c>
       <c r="M29" s="9" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="N29" s="10" t="inlineStr">
@@ -56443,7 +56603,7 @@
       </c>
       <c r="M30" s="9" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="N30" s="10" t="inlineStr">
@@ -56518,7 +56678,7 @@
       </c>
       <c r="M31" s="9" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="N31" s="10" t="inlineStr">
@@ -56593,7 +56753,7 @@
       </c>
       <c r="M32" s="9" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="N32" s="10" t="inlineStr">
@@ -56668,7 +56828,7 @@
       </c>
       <c r="M33" s="9" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="N33" s="10" t="inlineStr">
@@ -56970,10 +57130,14 @@
       </c>
       <c r="M6" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N6" s="10" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O6" s="9">
         <f>IF($M6="Terminada",$I6,0)</f>
         <v/>
@@ -57037,10 +57201,14 @@
       </c>
       <c r="M7" s="12" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N7" s="13" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="N7" s="13" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O7" s="12">
         <f>IF($M7="Terminada",$I7,0)</f>
         <v/>
@@ -57104,10 +57272,14 @@
       </c>
       <c r="M8" s="12" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N8" s="13" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="N8" s="13" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O8" s="12">
         <f>IF($M8="Terminada",$I8,0)</f>
         <v/>
@@ -57171,10 +57343,14 @@
       </c>
       <c r="M9" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N9" s="10" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
       <c r="O9" s="9">
         <f>IF($M9="Terminada",$I9,0)</f>
         <v/>
@@ -57238,10 +57414,14 @@
       </c>
       <c r="M10" s="12" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N10" s="13" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="N10" s="13" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O10" s="12">
         <f>IF($M10="Terminada",$I10,0)</f>
         <v/>
@@ -57305,10 +57485,14 @@
       </c>
       <c r="M11" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N11" s="10" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O11" s="9">
         <f>IF($M11="Terminada",$I11,0)</f>
         <v/>
@@ -57372,10 +57556,14 @@
       </c>
       <c r="M12" s="12" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N12" s="13" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="N12" s="13" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O12" s="12">
         <f>IF($M12="Terminada",$I12,0)</f>
         <v/>
@@ -57442,7 +57630,11 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="N13" s="10" t="n"/>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
       <c r="O13" s="9">
         <f>IF($M13="Terminada",$I13,0)</f>
         <v/>
@@ -57506,10 +57698,14 @@
       </c>
       <c r="M14" s="12" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N14" s="13" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="N14" s="13" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
       <c r="O14" s="12">
         <f>IF($M14="Terminada",$I14,0)</f>
         <v/>
@@ -57573,10 +57769,14 @@
       </c>
       <c r="M15" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N15" s="10" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O15" s="9">
         <f>IF($M15="Terminada",$I15,0)</f>
         <v/>
@@ -57640,10 +57840,14 @@
       </c>
       <c r="M16" s="12" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N16" s="13" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="N16" s="13" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
       <c r="O16" s="12">
         <f>IF($M16="Terminada",$I16,0)</f>
         <v/>
@@ -57707,10 +57911,14 @@
       </c>
       <c r="M17" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N17" s="10" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="N17" s="10" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
       <c r="O17" s="9">
         <f>IF($M17="Terminada",$I17,0)</f>
         <v/>
@@ -57774,10 +57982,14 @@
       </c>
       <c r="M18" s="12" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N18" s="13" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="N18" s="13" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O18" s="12">
         <f>IF($M18="Terminada",$I18,0)</f>
         <v/>
@@ -57844,7 +58056,11 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="N19" s="10" t="n"/>
+      <c r="N19" s="10" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
       <c r="O19" s="9">
         <f>IF($M19="Terminada",$I19,0)</f>
         <v/>
@@ -57908,10 +58124,14 @@
       </c>
       <c r="M20" s="12" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N20" s="13" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="N20" s="13" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
       <c r="O20" s="12">
         <f>IF($M20="Terminada",$I20,0)</f>
         <v/>
@@ -57975,10 +58195,14 @@
       </c>
       <c r="M21" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N21" s="10" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="N21" s="10" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O21" s="9">
         <f>IF($M21="Terminada",$I21,0)</f>
         <v/>
@@ -58045,7 +58269,11 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="N22" s="13" t="n"/>
+      <c r="N22" s="13" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
       <c r="O22" s="12">
         <f>IF($M22="Terminada",$I22,0)</f>
         <v/>
@@ -58109,10 +58337,14 @@
       </c>
       <c r="M23" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N23" s="10" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="N23" s="10" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
       <c r="O23" s="9">
         <f>IF($M23="Terminada",$I23,0)</f>
         <v/>
@@ -58176,10 +58408,14 @@
       </c>
       <c r="M24" s="12" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N24" s="13" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="N24" s="13" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O24" s="12">
         <f>IF($M24="Terminada",$I24,0)</f>
         <v/>
@@ -58502,10 +58738,14 @@
       </c>
       <c r="M6" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N6" s="10" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O6" s="9">
         <f>IF($M6="Terminada",$I6,0)</f>
         <v/>
@@ -58569,10 +58809,14 @@
       </c>
       <c r="M7" s="12" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N7" s="13" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="N7" s="13" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O7" s="12">
         <f>IF($M7="Terminada",$I7,0)</f>
         <v/>
@@ -58636,10 +58880,14 @@
       </c>
       <c r="M8" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N8" s="10" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O8" s="9">
         <f>IF($M8="Terminada",$I8,0)</f>
         <v/>
@@ -58703,10 +58951,14 @@
       </c>
       <c r="M9" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N9" s="10" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O9" s="9">
         <f>IF($M9="Terminada",$I9,0)</f>
         <v/>
@@ -58770,10 +59022,14 @@
       </c>
       <c r="M10" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N10" s="10" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O10" s="9">
         <f>IF($M10="Terminada",$I10,0)</f>
         <v/>
@@ -58840,7 +59096,11 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="N11" s="10" t="n"/>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O11" s="9">
         <f>IF($M11="Terminada",$I11,0)</f>
         <v/>
@@ -58904,10 +59164,14 @@
       </c>
       <c r="M12" s="12" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N12" s="13" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="N12" s="13" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O12" s="12">
         <f>IF($M12="Terminada",$I12,0)</f>
         <v/>
@@ -58971,10 +59235,14 @@
       </c>
       <c r="M13" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N13" s="10" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O13" s="9">
         <f>IF($M13="Terminada",$I13,0)</f>
         <v/>
@@ -59038,10 +59306,14 @@
       </c>
       <c r="M14" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="N14" s="10" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="N14" s="10" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O14" s="9">
         <f>IF($M14="Terminada",$I14,0)</f>
         <v/>
@@ -59108,7 +59380,11 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="N15" s="13" t="n"/>
+      <c r="N15" s="13" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
       <c r="O15" s="12">
         <f>IF($M15="Terminada",$I15,0)</f>
         <v/>
@@ -59175,7 +59451,11 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="N16" s="10" t="n"/>
+      <c r="N16" s="10" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
       <c r="O16" s="9">
         <f>IF($M16="Terminada",$I16,0)</f>
         <v/>
@@ -59242,7 +59522,11 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="N17" s="13" t="n"/>
+      <c r="N17" s="13" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O17" s="12">
         <f>IF($M17="Terminada",$I17,0)</f>
         <v/>
@@ -59309,7 +59593,11 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="N18" s="10" t="n"/>
+      <c r="N18" s="10" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
       <c r="O18" s="9">
         <f>IF($M18="Terminada",$I18,0)</f>
         <v/>
@@ -59376,7 +59664,11 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="N19" s="13" t="n"/>
+      <c r="N19" s="13" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
       <c r="O19" s="12">
         <f>IF($M19="Terminada",$I19,0)</f>
         <v/>
@@ -61333,7 +61625,11 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="N30" s="10" t="n"/>
+      <c r="N30" s="10" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O30" s="9">
         <f>IF($M30="Terminada",$I30,0)</f>
         <v/>
@@ -61404,7 +61700,11 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="N31" s="10" t="n"/>
+      <c r="N31" s="10" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O31" s="9">
         <f>IF($M31="Terminada",$I31,0)</f>
         <v/>
@@ -61475,7 +61775,11 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="N32" s="10" t="n"/>
+      <c r="N32" s="10" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
       <c r="O32" s="9">
         <f>IF($M32="Terminada",$I32,0)</f>
         <v/>
@@ -61546,7 +61850,11 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="N33" s="10" t="n"/>
+      <c r="N33" s="10" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
       <c r="O33" s="9">
         <f>IF($M33="Terminada",$I33,0)</f>
         <v/>
@@ -61617,7 +61925,11 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="N34" s="10" t="n"/>
+      <c r="N34" s="10" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
       <c r="O34" s="9">
         <f>IF($M34="Terminada",$I34,0)</f>
         <v/>
@@ -61688,7 +62000,11 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="N35" s="10" t="n"/>
+      <c r="N35" s="10" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
       <c r="O35" s="9">
         <f>IF($M35="Terminada",$I35,0)</f>
         <v/>
@@ -61759,7 +62075,11 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="N36" s="10" t="n"/>
+      <c r="N36" s="10" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O36" s="9">
         <f>IF($M36="Terminada",$I36,0)</f>
         <v/>
@@ -61901,7 +62221,11 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="N38" s="10" t="n"/>
+      <c r="N38" s="10" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O38" s="9">
         <f>IF($M38="Terminada",$I38,0)</f>
         <v/>
@@ -61972,7 +62296,11 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="N39" s="10" t="n"/>
+      <c r="N39" s="10" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O39" s="9">
         <f>IF($M39="Terminada",$I39,0)</f>
         <v/>
@@ -62043,7 +62371,11 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="N40" s="10" t="n"/>
+      <c r="N40" s="10" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O40" s="9">
         <f>IF($M40="Terminada",$I40,0)</f>
         <v/>
@@ -62114,7 +62446,11 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="N41" s="10" t="n"/>
+      <c r="N41" s="10" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O41" s="9">
         <f>IF($M41="Terminada",$I41,0)</f>
         <v/>
@@ -62185,7 +62521,11 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="N42" s="10" t="n"/>
+      <c r="N42" s="10" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="O42" s="9">
         <f>IF($M42="Terminada",$I42,0)</f>
         <v/>

--- a/Fase 2/SIGMA_Product_Backlog_por_Sprint.xlsx
+++ b/Fase 2/SIGMA_Product_Backlog_por_Sprint.xlsx
@@ -58599,6 +58599,7 @@
         <v/>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="27.75" customHeight="1" s="26">
       <c r="A5" s="8" t="inlineStr">
         <is>
@@ -59093,7 +59094,7 @@
       </c>
       <c r="M11" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="N11" s="10" t="inlineStr">
@@ -59519,7 +59520,7 @@
       </c>
       <c r="M17" s="12" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="N17" s="13" t="inlineStr">

--- a/Fase 2/SIGMA_Product_Backlog_por_Sprint.xlsx
+++ b/Fase 2/SIGMA_Product_Backlog_por_Sprint.xlsx
@@ -58599,7 +58599,6 @@
         <v/>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="27.75" customHeight="1" s="26">
       <c r="A5" s="8" t="inlineStr">
         <is>
@@ -59378,7 +59377,7 @@
       </c>
       <c r="M15" s="12" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="N15" s="13" t="inlineStr">
@@ -59390,7 +59389,11 @@
         <f>IF($M15="Terminada",$I15,0)</f>
         <v/>
       </c>
-      <c r="P15" s="13" t="n"/>
+      <c r="P15" s="13" t="inlineStr">
+        <is>
+          <t>Galería de evidencias en la ficha de la OT y del activo (web) y GET /api/archivo-vinculos para la app (BD/429–436). Tareas de Catalina terminadas; el consumo desde la app (T-5257) pasó al Sprint 6. Pendiente validación de la PO.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="30" customHeight="1" s="26">
       <c r="A16" s="9" t="inlineStr">
@@ -59449,7 +59452,7 @@
       </c>
       <c r="M16" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En curso</t>
         </is>
       </c>
       <c r="N16" s="10" t="inlineStr">
@@ -59461,7 +59464,11 @@
         <f>IF($M16="Terminada",$I16,0)</f>
         <v/>
       </c>
-      <c r="P16" s="10" t="n"/>
+      <c r="P16" s="10" t="inlineStr">
+        <is>
+          <t>Modelo revisado y referencias ya separadas en las galerías del activo y de la OT. Falta adjuntar la referencia desde la actividad del plan y el ítem de pauta (T-5262 a T-5276).</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="30" customHeight="1" s="26">
       <c r="A17" s="12" t="inlineStr">

--- a/Fase 2/SIGMA_Product_Backlog_por_Sprint.xlsx
+++ b/Fase 2/SIGMA_Product_Backlog_por_Sprint.xlsx
@@ -59452,7 +59452,7 @@
       </c>
       <c r="M16" s="9" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="N16" s="10" t="inlineStr">
@@ -59466,7 +59466,7 @@
       </c>
       <c r="P16" s="10" t="inlineStr">
         <is>
-          <t>Modelo revisado y referencias ya separadas en las galerías del activo y de la OT. Falta adjuntar la referencia desde la actividad del plan y el ítem de pauta (T-5262 a T-5276).</t>
+          <t>Imagen de referencia en la actividad del plan y en el ítem de pauta; la ve quien ejecuta en la OT y en la inspección (BD/454). Pendiente validación de la PO.</t>
         </is>
       </c>
     </row>
